--- a/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-PR-PractitionerRole.xlsx
+++ b/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-PR-PractitionerRole.xlsx
@@ -439,7 +439,7 @@
     <t>PractitionerRole.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -477,7 +477,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -511,7 +511,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -554,7 +554,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -793,7 +793,7 @@
     <t>The role a person plays representing an organization.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/practitioner-role</t>
+    <t>http://hl7.org/fhir/ValueSet/practitioner-role|4.0.1</t>
   </si>
   <si>
     <t>PRD-1 / STF-18  / PRA-3  / PRT-4  / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17</t>
@@ -817,7 +817,7 @@
     <t>Specific specialty associated with the agency.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|4.0.1</t>
   </si>
   <si>
     <t>PRA-5</t>
@@ -832,7 +832,7 @@
     <t>PractitionerRole.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -854,7 +854,7 @@
     <t>PractitionerRole.healthcareService</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(HealthcareService)
+    <t xml:space="preserve">Reference(HealthcareService|4.0.1)
 </t>
   </si>
   <si>
@@ -1181,7 +1181,7 @@
     <t>PractitionerRole.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -6335,7 +6335,7 @@
         <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>100</v>
@@ -6449,7 +6449,7 @@
         <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>100</v>
